--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488247_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488247_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. ARANDA SUAREZ</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7371</v>
+        <v>7.5269</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8796</v>
+        <v>6.1432</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8576</v>
+        <v>1.3837</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6848</v>
+        <v>4.0674</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9812</v>
+        <v>0.7956</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7036</v>
+        <v>3.2717</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8054</v>
+        <v>2.8366</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5151</v>
+        <v>0.1718</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2903</v>
+        <v>2.6648</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8794999999999999</v>
+        <v>1.2307</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5338000000000001</v>
+        <v>0.6239</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4133</v>
+        <v>0.6069</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1117</v>
+        <v>-0.1853</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4823</v>
+        <v>0.9264</v>
       </c>
       <c r="S2" t="n">
-        <v>5.9411</v>
+        <v>-0.4287</v>
       </c>
       <c r="T2" t="n">
-        <v>5.872</v>
+        <v>0.3448</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06909999999999999</v>
+        <v>-0.7735</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.2594</v>
+        <v>3.1471</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3139</v>
+        <v>3.1471</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>X. NEWSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0854</v>
+        <v>4.3505</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8495</v>
+        <v>2.4219</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2359</v>
+        <v>1.9286</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0674</v>
+        <v>2.0329</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7956</v>
+        <v>-3.1186</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2717</v>
+        <v>5.1515</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8366</v>
+        <v>1.3043</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1718</v>
+        <v>-1.9116</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6648</v>
+        <v>3.2159</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2307</v>
+        <v>0.7286</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6239</v>
+        <v>-1.207</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6069</v>
+        <v>1.9356</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7411</v>
+        <v>1.1117</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1853</v>
+        <v>-1.1117</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9264</v>
+        <v>2.2234</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8702</v>
+        <v>-0.3675</v>
       </c>
       <c r="T3" t="n">
-        <v>0.051</v>
+        <v>0.656</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9212</v>
+        <v>-1.0235</v>
       </c>
       <c r="V3" t="n">
-        <v>3.1471</v>
+        <v>1.5733</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1471</v>
+        <v>1.5733</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. NEWSON</t>
+          <t>C. ARANDA SUAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0041</v>
+        <v>3.6952</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0508</v>
+        <v>3.2562</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9532</v>
+        <v>0.439</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0329</v>
+        <v>2.6848</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.1186</v>
+        <v>0.9812</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1515</v>
+        <v>1.7036</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3043</v>
+        <v>1.8054</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.9116</v>
+        <v>1.5151</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2159</v>
+        <v>0.2903</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7286</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.207</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>1.9356</v>
+        <v>1.4133</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1117</v>
+        <v>0.3706</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1117</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2234</v>
+        <v>1.4823</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7139</v>
+        <v>1.8992</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.715</v>
+        <v>2.2487</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9988</v>
+        <v>-0.3495</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5733</v>
+        <v>-1.2594</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5733</v>
+        <v>0.3139</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VARO BARBANCHO</t>
+          <t>P. VILLAREJO CALATAYUD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2059</v>
+        <v>2.6804</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7516</v>
+        <v>1.164</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4543</v>
+        <v>1.5164</v>
       </c>
       <c r="G5" t="n">
-        <v>2.552</v>
+        <v>3.9724</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0591</v>
+        <v>2.4042</v>
       </c>
       <c r="I5" t="n">
-        <v>1.493</v>
+        <v>1.5681</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0063</v>
+        <v>3.789</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7514999999999999</v>
+        <v>3.6112</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2548</v>
+        <v>0.1778</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5457</v>
+        <v>0.1833</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3076</v>
+        <v>-1.207</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2381</v>
+        <v>1.3903</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1853</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>-2.9646</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1117</v>
+        <v>2.4087</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5325</v>
+        <v>-0.4222</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3283</v>
+        <v>0.3401</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2042</v>
+        <v>-0.7623</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0011</v>
+        <v>-0.3139</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0011</v>
+        <v>-0.3133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>J. VARO BARBANCHO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1643</v>
+        <v>2.2541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8155</v>
+        <v>0.9474</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3489</v>
+        <v>1.3066</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2646</v>
+        <v>2.552</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5995</v>
+        <v>1.0591</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6652</v>
+        <v>1.493</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3079</v>
+        <v>2.0063</v>
       </c>
       <c r="K6" t="n">
-        <v>1.142</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1659</v>
+        <v>1.2548</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0433</v>
+        <v>0.5457</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5426</v>
+        <v>0.3076</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4993</v>
+        <v>0.2381</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9264</v>
+        <v>0.1853</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7123</v>
+        <v>-0.4844</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4924</v>
+        <v>-0.1324</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2199</v>
+        <v>-0.3519</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3144</v>
+        <v>0.0011</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3144</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. VILLAREJO CALATAYUD</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9423</v>
+        <v>1.9724</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5987</v>
+        <v>1.5989</v>
       </c>
       <c r="F7" t="n">
-        <v>1.541</v>
+        <v>0.3735</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9724</v>
+        <v>1.2646</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4042</v>
+        <v>0.5995</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5681</v>
+        <v>0.6652</v>
       </c>
       <c r="J7" t="n">
-        <v>3.789</v>
+        <v>1.3079</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6112</v>
+        <v>1.142</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1778</v>
+        <v>0.1659</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1833</v>
+        <v>-0.0433</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.207</v>
+        <v>-0.5426</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3903</v>
+        <v>0.4993</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9646</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4087</v>
+        <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.1603</v>
+        <v>0.0958</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4226</v>
+        <v>0.291</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7377</v>
+        <v>-0.1952</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3139</v>
+        <v>-0.3144</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3133</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8701</v>
+        <v>-0.3531</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9086</v>
+        <v>0.5376</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0385</v>
+        <v>-0.8908</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2177</v>
@@ -1078,13 +1078,13 @@
         <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2911</v>
+        <v>0.0678</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8454</v>
+        <v>0.4744</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5544</v>
+        <v>-0.4066</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9444</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8425</v>
+        <v>-0.6954</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2971</v>
+        <v>0.395</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1396</v>
+        <v>-1.0903</v>
       </c>
       <c r="G9" t="n">
         <v>0.6446</v>
@@ -1156,13 +1156,13 @@
         <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5989</v>
+        <v>-0.4517</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4895</v>
+        <v>-0.4402</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2589</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0361</v>
+        <v>-2.9382</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2113</v>
+        <v>-1.1134</v>
       </c>
       <c r="F10" t="n">
         <v>-1.8248</v>
@@ -1234,10 +1234,10 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4253</v>
+        <v>-0.3274</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2151</v>
+        <v>0.3131</v>
       </c>
       <c r="U10" t="n">
         <v>-0.6404</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5485</v>
+        <v>-3.5676</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9745</v>
+        <v>-4.289</v>
       </c>
       <c r="F11" t="n">
-        <v>0.426</v>
+        <v>0.7214</v>
       </c>
       <c r="G11" t="n">
         <v>-3.4228</v>
@@ -1312,13 +1312,13 @@
         <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2555</v>
+        <v>-0.2745</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2773</v>
+        <v>0.4082</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9782</v>
+        <v>-0.6827</v>
       </c>
       <c r="V11" t="n">
         <v>0.315</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5592</v>
+        <v>-5.9023</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2327</v>
+        <v>-2.5265</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3265</v>
+        <v>-3.3758</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6934</v>
@@ -1390,13 +1390,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>0.763</v>
+        <v>0.42</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0321</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2691</v>
+        <v>-0.3184</v>
       </c>
       <c r="V12" t="n">
         <v>-3.1466</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.022899999999996</v>
+        <v>9.022900000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>8.535500000000001</v>
+        <v>8.535300000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4875000000000003</v>
+        <v>0.4874999999999998</v>
       </c>
       <c r="G13" t="n">
         <v>10.9034</v>
@@ -1444,7 +1444,7 @@
         <v>7.375300000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>4.496899999999998</v>
+        <v>4.4969</v>
       </c>
       <c r="L13" t="n">
         <v>2.878299999999999</v>
@@ -1453,10 +1453,10 @@
         <v>3.528</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.382000000000001</v>
+        <v>-5.382</v>
       </c>
       <c r="O13" t="n">
-        <v>8.910000000000002</v>
+        <v>8.91</v>
       </c>
       <c r="P13" t="n">
         <v>1.8527</v>
@@ -1468,13 +1468,13 @@
         <v>12.97</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2736999999999997</v>
+        <v>-0.2736000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>5.670599999999999</v>
+        <v>5.6708</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.9443</v>
+        <v>-5.944199999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-3.46</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2249</v>
+        <v>2.8869</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8737</v>
+        <v>1.3633</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3512</v>
+        <v>1.5236</v>
       </c>
       <c r="G14" t="n">
         <v>1.4475</v>
@@ -1546,13 +1546,13 @@
         <v>0.3706</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2221</v>
+        <v>0.4399</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2189</v>
+        <v>0.2708</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0032</v>
+        <v>0.1691</v>
       </c>
       <c r="V14" t="n">
         <v>0.6289</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1444</v>
+        <v>1.7532</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8948</v>
+        <v>2.4052</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7504</v>
+        <v>-0.6519</v>
       </c>
       <c r="G15" t="n">
         <v>2.4646</v>
@@ -1624,13 +1624,13 @@
         <v>2.0382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0226</v>
+        <v>-0.4138</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2983</v>
+        <v>0.8086</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3209</v>
+        <v>-1.2224</v>
       </c>
       <c r="V15" t="n">
         <v>0.6289</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. RUIZ CORDAL</t>
+          <t>J. PINA GUISADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1064</v>
+        <v>1.4851</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2608</v>
+        <v>1.8629</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8456</v>
+        <v>-0.3778</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.0422</v>
+        <v>1.3462</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.789</v>
+        <v>-0.408</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2532</v>
+        <v>1.7541</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.6104</v>
+        <v>1.9292</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.0404</v>
+        <v>0.0215</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5699</v>
+        <v>1.9077</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4318</v>
+        <v>-0.583</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.4294</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6833</v>
+        <v>-0.1536</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9646</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8529</v>
+        <v>0.1853</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5393</v>
+        <v>-0.0463</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1153</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.424</v>
+        <v>0.0199</v>
       </c>
       <c r="V16" t="n">
-        <v>4.721</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>4.7204</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PINA GUISADO</t>
+          <t>C. GALAN PLAZA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4611</v>
+        <v>1.267</v>
       </c>
       <c r="E17" t="n">
-        <v>1.765</v>
+        <v>1.5826</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3039</v>
+        <v>-0.3156</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3462</v>
+        <v>-0.411</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.408</v>
+        <v>-0.4294</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7541</v>
+        <v>0.0185</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9292</v>
+        <v>0.0415</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0215</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9077</v>
+        <v>0.0415</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.583</v>
+        <v>-0.4524</v>
       </c>
       <c r="N17" t="n">
         <v>-0.4294</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1536</v>
+        <v>-0.023</v>
       </c>
       <c r="P17" t="n">
         <v>0.1853</v>
@@ -1780,19 +1780,19 @@
         <v>0.1853</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0704</v>
+        <v>0.2338</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1641</v>
+        <v>0.2823</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09379999999999999</v>
+        <v>-0.0485</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. GALAN PLAZA</t>
+          <t>J. RUIZ CORDAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.826</v>
+        <v>0.7326</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1909</v>
+        <v>0.3794</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3649</v>
+        <v>0.3532</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.411</v>
+        <v>-4.0422</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4294</v>
+        <v>-2.789</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0185</v>
+        <v>-1.2532</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0415</v>
+        <v>-2.6104</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-2.0404</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0415</v>
+        <v>-0.5699</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4524</v>
+        <v>-1.4318</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4294</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.023</v>
+        <v>-0.6833</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1853</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.9646</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1853</v>
+        <v>1.8529</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2072</v>
+        <v>1.1655</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1094</v>
+        <v>1.2339</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0977</v>
+        <v>-0.0684</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2589</v>
+        <v>4.721</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2589</v>
+        <v>4.7204</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. REMESAL LEÓN</t>
+          <t>M. TRILLO MANGANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3221</v>
+        <v>0.3531</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3221</v>
+        <v>0.2033</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.1499</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3221</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3221</v>
+        <v>0.0284</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0.1121</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3221</v>
+        <v>-0.4698</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3221</v>
+        <v>0.1416</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.3862</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.1131</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.4993</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.6731</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.6069</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. TRILLO MANGANO</t>
+          <t>J. REMESAL LEÓN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0391</v>
+        <v>0.3221</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0905</v>
+        <v>0.3221</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0514</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.08359999999999999</v>
+        <v>0.3221</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0284</v>
+        <v>0.3221</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1121</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4698</v>
+        <v>0.3221</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1416</v>
+        <v>0.3221</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1131</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4993</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3261</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3793</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7053</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>D. CASTRO DIANEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0095</v>
+        <v>-1.8208</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0672</v>
+        <v>-0.8873</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0577</v>
+        <v>-0.9335</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.103</v>
+        <v>-2.3673</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6883</v>
+        <v>-0.7068</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4147</v>
+        <v>-1.6605</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1903</v>
+        <v>-1.2013</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5374</v>
+        <v>0.0215</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6529</v>
+        <v>-1.2228</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0873</v>
+        <v>-1.166</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1508</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2381</v>
+        <v>-0.4377</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.4823</v>
+        <v>0.3706</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9458</v>
+        <v>0.176</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0321</v>
+        <v>0.314</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0863</v>
+        <v>-0.138</v>
       </c>
       <c r="V21" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. CASTRO DIANEZ</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4822</v>
+        <v>-1.9177</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4749</v>
+        <v>-1.5568</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0073</v>
+        <v>-0.3609</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3673</v>
+        <v>-1.103</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7068</v>
+        <v>-0.6883</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6605</v>
+        <v>-0.4147</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2013</v>
+        <v>-1.1903</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0215</v>
+        <v>-0.5374</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2228</v>
+        <v>-0.6529</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.166</v>
+        <v>0.0873</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.1508</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4377</v>
+        <v>0.2381</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3706</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R22" t="n">
         <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4855</v>
+        <v>0.0376</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2736</v>
+        <v>0.5425</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2119</v>
+        <v>-0.5049</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. REMESAL LEON</t>
+          <t>M. EZOMO GERVILLA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1245</v>
+        <v>-3.5421</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6552</v>
+        <v>-2.1451</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.7797</v>
+        <v>-1.3971</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.9888</v>
+        <v>-3.2161</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4496</v>
+        <v>0.4289</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5392</v>
+        <v>-3.645</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1128</v>
+        <v>-1.3548</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1033</v>
+        <v>1.2151</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0095</v>
+        <v>-2.57</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8759</v>
+        <v>-1.8612</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3463</v>
+        <v>-0.7863</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-1.075</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9646</v>
+        <v>-0.1853</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6676</v>
+        <v>1.8529</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4207</v>
+        <v>-0.7337</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5304</v>
+        <v>0.0261</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1098</v>
+        <v>-0.7598</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2594</v>
+        <v>-1.26</v>
       </c>
       <c r="W23" t="n">
-        <v>2.2022</v>
+        <v>-0.6311</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.4616</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. EZOMO GERVILLA</t>
+          <t>M. CABEZA RUEDA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0373</v>
+        <v>-4.1889</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3202</v>
+        <v>-2.6158</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7171</v>
+        <v>-1.5731</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.2161</v>
+        <v>-1.2719</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4289</v>
+        <v>0.1718</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.645</v>
+        <v>-1.4437</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3548</v>
+        <v>-0.9628</v>
       </c>
       <c r="K24" t="n">
-        <v>1.2151</v>
+        <v>0.3429</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.57</v>
+        <v>-1.3057</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8612</v>
+        <v>-0.3091</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7863</v>
+        <v>-0.1711</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.075</v>
+        <v>-0.138</v>
       </c>
       <c r="P24" t="n">
-        <v>1.6676</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1853</v>
+        <v>-2.0382</v>
       </c>
       <c r="R24" t="n">
         <v>1.8529</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.2289</v>
+        <v>-0.8434</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.149</v>
+        <v>0.3852</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0799</v>
+        <v>-1.2286</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.26</v>
+        <v>-1.8883</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6311</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6289</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. CABEZA RUEDA</t>
+          <t>J. REMESAL LEON</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.415</v>
+        <v>-6.3534</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4972</v>
+        <v>-1.4013</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9178</v>
+        <v>-4.952</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.2719</v>
+        <v>-3.9888</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1718</v>
+        <v>-1.4496</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4437</v>
+        <v>-2.5392</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9628</v>
+        <v>-2.1128</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3429</v>
+        <v>-0.1033</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3057</v>
+        <v>-2.0095</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3091</v>
+        <v>-1.8759</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1711</v>
+        <v>-1.3463</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.138</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1853</v>
+        <v>-1.297</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.0382</v>
+        <v>-2.9646</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.0695</v>
+        <v>0.1918</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4961</v>
+        <v>1.4739</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.5733</v>
+        <v>-1.2821</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.8883</v>
+        <v>-1.2594</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.2022</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.8883</v>
+        <v>-3.4616</v>
       </c>
     </row>
     <row r="26">
@@ -2437,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.0227</v>
+        <v>-9.0229</v>
       </c>
       <c r="E26" t="n">
         <v>-0.4875000000000003</v>
@@ -2449,7 +2449,7 @@
         <v>-10.9035</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8849999999999998</v>
+        <v>0.885</v>
       </c>
       <c r="I26" t="n">
         <v>-11.7886</v>
@@ -2482,22 +2482,22 @@
         <v>11.1175</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2735000000000003</v>
+        <v>0.2736</v>
       </c>
       <c r="T26" t="n">
-        <v>5.944299999999999</v>
+        <v>5.944199999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.6705</v>
+        <v>-5.6706</v>
       </c>
       <c r="V26" t="n">
-        <v>3.459999999999999</v>
+        <v>3.46</v>
       </c>
       <c r="W26" t="n">
         <v>10.0665</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.606599999999999</v>
+        <v>-6.6066</v>
       </c>
     </row>
   </sheetData>
